--- a/Filtered_V3.0/COCKN_HCAFlorida_Kendall_Hospital.xlsx
+++ b/Filtered_V3.0/COCKN_HCAFlorida_Kendall_Hospital.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Abstracting </t>
+          <t>3M (360 Encompass)-ABSDPI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Admissions </t>
+          <t>3M (360 Encompass)-ADMO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Charges </t>
+          <t>3M (360 Encompass)-ITSDIRO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS DI Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-ITSHMRO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-ITS HM Results </t>
+          <t>3M (360 Encompass)-LABRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-Lab Results (Discrete) </t>
+          <t>3M (360 Encompass)-OMORDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3M (360 Encompass)-OM Orders </t>
+          <t>3M (360 Encompass)-Patient Accounting</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople ED Patient Visit Data</t>
+          <t>3M (360 Encompass)-iPeople EDM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Medication Administration</t>
+          <t>3M (360 Encompass)-iPeople Meds</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3M (360 Encompass)-iPeople Nursing Assessment Forms</t>
+          <t>3M (360 Encompass)-iPeople PCS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-Admissions </t>
+          <t>AQuity Solutions (DocEP)-ADMO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AQuity Solutions (DocEP)-ITS HM Results </t>
+          <t>AQuity Solutions (DocEP)-ITSHMRO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Airstrip Technologies (ONE)-Admissions </t>
+          <t>Airstrip Technologies (ONE)-ADMO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alere (MAS RALS-Plus)-</t>
+          <t>Alere (MAS RALS-Plus)-ADMO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1997,7 +1997,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -2019,7 +2034,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alere (MAS RALS-Plus)-Admissions </t>
+          <t>Alere (MAS RALS-Plus)-labpoc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2064,22 +2079,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AngelEye (NICU CameraSystem)-Admissions </t>
+          <t>AngelEye (NICU CameraSystem)-ADMO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Admissions </t>
+          <t>BD (Pyxis Medstation ES)-ADMO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Inventory </t>
+          <t>BD (Pyxis Medstation ES)-PHAINV</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD (Pyxis Medstation ES)-Pharmacy Orders </t>
+          <t>BD (Pyxis Medstation ES)-PHAORD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-Admissions </t>
+          <t>Computrition (Computrition)-ADMO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computrition (Computrition)-OM Orders </t>
+          <t>Computrition (Computrition)-OMORDO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Datavant/CIOX (HealthSource to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion Voice)-Admissions </t>
+          <t>Dolbey (Fusion Voice)-ADMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dolbey (Fusion)-</t>
+          <t>Dolbey (Fusion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3159,7 +3159,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ITSDIRO</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3181,7 +3196,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolbey (Fusion)-ITS DI Results </t>
+          <t>Dolbey (Fusion)-radord</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3226,22 +3241,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Admissions </t>
+          <t>Envision Healthcare (Envision Healthcare)-ADMO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS DI Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-CWSO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSDIRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-ITS HM Results </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Envision Healthcare (Envision Healthcare)-Scheduling </t>
+          <t>Envision Healthcare (Envision Healthcare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3698,22 +3698,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Envision Healthcare (Envision Healthcare)-iPeople ED Patient Visit Data</t>
+          <t>Envision Healthcare (Envision Healthcare)-iPeople EDM</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Florida HIE (Event Notification Service)-Admissions </t>
+          <t>Florida HIE (Event Notification Service)-ADMO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Admissions </t>
+          <t>GE (CMI - Carescape Gateway)-ADMO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CMI - Carescape Gateway)-Scheduling </t>
+          <t>GE (CMI - Carescape Gateway)-CWSO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Admissions </t>
+          <t>GE (CPN - Gold Standard)-ADMO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Clinical Monitoring Results </t>
+          <t>GE (CPN - Gold Standard)-ITSHMRO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PCSCMI</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical Monitoring Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-ITS HM Results </t>
+          <t>GE (CPN - Gold Standard)-LABRES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (CPN - Gold Standard)-Lab Results (Discrete) </t>
+          <t>GE (CPN - Gold Standard)-PCSCMI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>PCSCMI</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">Clinical Monitoring Results </t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GE (Centricity - CCG PACS)-</t>
+          <t>GE (Centricity - CCG PACS)-ADMO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4685,6 +4685,21 @@
       <c r="P56" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -4706,7 +4721,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Admissions </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIRO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4756,17 +4771,17 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -4788,7 +4803,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-ITS DI Results </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4833,22 +4848,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSDIUI</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Radiology Image Status </t>
         </is>
       </c>
     </row>
@@ -4870,7 +4885,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-ITSDIUI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4952,7 +4967,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity - CCG PACS)-Radiology Image Status </t>
+          <t>GE (Centricity - CCG PACS)-radord</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4997,22 +5012,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>ITSDIUI</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>ORM</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Radiology Image Status </t>
+          <t>Outbound</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW to Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity Cardio Workflow-CCW to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Admissions </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ADMO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-Charges </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-ITSHMRO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-ITS HM Results </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-OMORDO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5578,22 +5578,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity Cardio Workflow-CCW)-OM Orders </t>
+          <t>GE (Centricity Cardio Workflow-CCW)-Patient Accounting</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5660,22 +5660,22 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Centricity MUSE to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Admissions </t>
+          <t>GE (Centricity MUSE)-ADMO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-Charges </t>
+          <t>GE (Centricity MUSE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6035,17 +6035,17 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-ITS HM Results </t>
+          <t>GE (Centricity MUSE)-OMORDO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Centricity MUSE)-OM Orders </t>
+          <t>GE (Centricity MUSE)-Patient Accounting</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6194,22 +6194,22 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>GE (Centricity MacLab-DMS/CVPACS to MPF-Patient Folder/HPF Facility)-</t>
+          <t>GE (Centricity MacLab-DMS/CVPACS to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>GE (Edison Datalogue to MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-</t>
+          <t>Google (Healthcare Data Engine - HDE)-ADMO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6612,6 +6612,21 @@
       <c r="P82" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -6633,7 +6648,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Admissions </t>
+          <t>Google (Healthcare Data Engine - HDE)-CWSO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6683,17 +6698,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6730,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS DI Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-IMMUN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6765,17 +6780,17 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6812,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-ITS HM Results </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSDIRO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6847,7 +6862,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -6857,7 +6872,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -6879,7 +6894,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Lab Results (Discrete) </t>
+          <t>Google (Healthcare Data Engine - HDE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6929,7 +6944,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -6939,7 +6954,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -6961,7 +6976,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-MU-Immunizations</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7011,17 +7026,17 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -7043,7 +7058,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-Pathology Results</t>
+          <t>Google (Healthcare Data Engine - HDE)-LABRES2</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7125,7 +7140,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Pharmacy Orders </t>
+          <t>Google (Healthcare Data Engine - HDE)-PHAORD</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7207,7 +7222,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google (Healthcare Data Engine - HDE)-Scheduling </t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople EDM</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7257,17 +7272,17 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7304,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople ED Patient Visit Data</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople Meds</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7339,17 +7354,17 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7386,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Medication Administration</t>
+          <t>Google (Healthcare Data Engine - HDE)-iPeople PCS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7421,17 +7436,17 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7453,7 +7468,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Google (Healthcare Data Engine - HDE)-iPeople Nursing Assessment Forms</t>
+          <t>Google (Healthcare Data Engine - HDE)-radord</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7499,21 +7514,6 @@
       <c r="P93" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-ADMO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7643,6 +7643,21 @@
       <c r="P95" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -7664,7 +7679,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-</t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7710,6 +7725,21 @@
       <c r="P96" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>CWSO</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>iPeople Scheduling</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7761,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Admissions </t>
+          <t>HCA (Cloudera Kafka)-CWSO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7781,17 +7811,17 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -7813,7 +7843,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-IMMUN</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7863,17 +7893,17 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7925,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS DI Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7977,7 +8007,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-ITS HM Results </t>
+          <t>HCA (Cloudera Kafka)-ITSDIRO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8027,7 +8057,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -8037,7 +8067,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -8059,7 +8089,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-ITSHMRO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8109,7 +8139,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -8119,7 +8149,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -8141,7 +8171,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Lab Results (Discrete) </t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -8223,7 +8253,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-MU-Immunizations</t>
+          <t>HCA (Cloudera Kafka)-LABRES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -8273,17 +8303,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -8305,7 +8335,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-OM Orders </t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8355,17 +8385,17 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8417,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-LABRES2</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8469,7 +8499,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-Pathology Results</t>
+          <t>HCA (Cloudera Kafka)-OMORDO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8519,17 +8549,17 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8581,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Pharmacy Orders </t>
+          <t>HCA (Cloudera Kafka)-PHAORD</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8633,7 +8663,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8683,17 +8713,17 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8745,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Cloudera Kafka)-Scheduling </t>
+          <t>HCA (Cloudera Kafka)-iPeople EDM</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8765,17 +8795,17 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8827,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople Meds</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8847,17 +8877,17 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8909,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople ED Patient Visit Data</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8929,17 +8959,17 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8991,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Medication Administration</t>
+          <t>HCA (Cloudera Kafka)-iPeople PCS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -9011,17 +9041,17 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9073,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -9089,21 +9119,6 @@
       <c r="P113" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9125,7 +9140,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>HCA (Cloudera Kafka)-iPeople Nursing Assessment Forms</t>
+          <t>HCA (Cloudera Kafka)-radord</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9171,21 +9186,6 @@
       <c r="P114" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (EDW CDM)-Scheduling </t>
+          <t>HCA (EDW CDM)-CWSO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (Revive)-ITS HM Results </t>
+          <t>HCA (Revive)-ITSHMRO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HCA (SMART to Optiflex)-</t>
+          <t>HCA (SMART to Optiflex)-multi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-ADMO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9731,7 +9731,22 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -9753,7 +9768,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HCA (SMART)-</t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9820,7 +9835,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA (SMART)-Admissions </t>
+          <t>HCA (SMART)-multi</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9865,22 +9880,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ADMO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10010,6 +10010,21 @@
       <c r="P126" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -10031,7 +10046,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Admissions </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10081,17 +10096,17 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10128,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS DI Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-CWSO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -10163,17 +10178,17 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -10195,7 +10210,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-ITS HM Results </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-IMMUN</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10245,17 +10260,17 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10292,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSDIRO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -10327,7 +10342,7 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -10337,7 +10352,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -10359,7 +10374,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Electronic Lab Reporting</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-ITSHMRO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -10409,7 +10424,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>PHELR</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -10419,7 +10434,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>MU-Electronic Lab Reporting</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -10441,7 +10456,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -10491,17 +10506,17 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -10523,7 +10538,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-LABRES2</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10573,17 +10588,17 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10620,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10687,7 +10702,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-OM Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-OMORDO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10769,7 +10784,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-Pathology Results</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHAORD</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10819,17 +10834,17 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -10851,7 +10866,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHELR</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10901,17 +10916,17 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>PHELR</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>MU-Electronic Lab Reporting</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10948,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-PHSS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10983,17 +10998,17 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -11015,7 +11030,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (EIS Biztalk Platform)-Scheduling </t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople EDM</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11065,17 +11080,17 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11112,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Meds</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -11147,17 +11162,17 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11194,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople PCS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -11229,17 +11244,17 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11276,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (EIS Biztalk Platform)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (EIS Biztalk Platform)-radord</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -11307,21 +11322,6 @@
       <c r="P142" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (FHIR Web Services)-Admissions </t>
+          <t>HCA D&amp;IS (FHIR Web Services)-ADMO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (HCA 5.6)-ITS HM Results </t>
+          <t>HCA D&amp;IS (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-</t>
+          <t>HCA D&amp;IS (MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Null-Terminates Message)-</t>
+          <t>HCA D&amp;IS (Null-Terminates Message)-iti08</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-</t>
+          <t>HCA D&amp;IS (Waterpark)-ADMO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -12079,6 +12079,21 @@
       <c r="P153" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -12100,7 +12115,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Admissions </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12150,17 +12165,17 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>iPeople Scheduling</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>SIU</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12197,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS DI Results </t>
+          <t>HCA D&amp;IS (Waterpark)-CWSO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -12232,17 +12247,17 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -12264,7 +12279,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-ITS HM Results </t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -12314,17 +12329,17 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12361,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Immunization Query</t>
+          <t>HCA D&amp;IS (Waterpark)-IMMUNQRY</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -12428,7 +12443,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Lab Results (Discrete) </t>
+          <t>HCA D&amp;IS (Waterpark)-ITSDIRO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12478,7 +12493,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -12488,7 +12503,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -12510,7 +12525,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Immunizations</t>
+          <t>HCA D&amp;IS (Waterpark)-ITSHMRO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12560,17 +12575,17 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -12592,7 +12607,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-MU-Syndromic Surveillance</t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12642,17 +12657,17 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>PHSS</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>MU-Syndromic Surveillance</t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -12674,7 +12689,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-LABRES2</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12724,17 +12739,17 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>iPeople OM Orders</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>ORM - iPeople</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12771,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-OM Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12811,12 +12826,12 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>iPeople OM Orders</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t>ORM - iPeople</t>
         </is>
       </c>
     </row>
@@ -12838,7 +12853,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-Pathology Results</t>
+          <t>HCA D&amp;IS (Waterpark)-OMORDO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12888,17 +12903,17 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -12920,7 +12935,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Pharmacy Orders </t>
+          <t>HCA D&amp;IS (Waterpark)-PHAORD</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -13002,7 +13017,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-PHSS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -13052,17 +13067,17 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>PHSS</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>iPeople Scheduling</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>MU-Syndromic Surveillance</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13099,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA D&amp;IS (Waterpark)-Scheduling </t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople EDM</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13134,17 +13149,17 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13181,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople ED Patient Visit Data</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople Meds</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13216,17 +13231,17 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople Meds</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>RAS - iPeople</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Medication Administration</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13263,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Medication Administration</t>
+          <t>HCA D&amp;IS (Waterpark)-iPeople PCS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13298,17 +13313,17 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>iPeople Meds</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>RAS - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>iPeople Medication Administration</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13345,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>HCA D&amp;IS (Waterpark)-iPeople Nursing Assessment Forms</t>
+          <t>HCA D&amp;IS (Waterpark)-radord</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13376,21 +13391,6 @@
       <c r="P169" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (Charge Master)-SMART Procedure Codes </t>
+          <t>HCA Parallon (Charge Master)-MISPROC</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">HCA Parallon (eCapture)-Admissions </t>
+          <t>HCA Parallon (eCapture)-ADMO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Healogics (iHeal/NetHealth WoundExpert)-Admissions </t>
+          <t>Healogics (iHeal/NetHealth WoundExpert)-ADMO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Healogics (iHeal/NetHealth WoundExpert)-Charges </t>
+          <t>Healogics (iHeal/NetHealth WoundExpert)-ITSHMRO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13894,17 +13894,17 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Healogics (iHeal/NetHealth WoundExpert)-ITS HM Results </t>
+          <t>Healogics (iHeal/NetHealth WoundExpert)-Patient Accounting</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13976,17 +13976,17 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Admissions </t>
+          <t>Health Catalyst (HCare Hub)-ADMO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS DI Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSDIRO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-ITS HM Results </t>
+          <t>Health Catalyst (HCare Hub)-ITSHMRO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Catalyst (HCare Hub)-Lab Results (Discrete) </t>
+          <t>Health Catalyst (HCare Hub)-LABRES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Health Catalyst (HCare Hub)-Pathology Results</t>
+          <t>Health Catalyst (HCare Hub)-LABRES2</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Admissions </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-ADMO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hill-Rom/Welch Allyn (Connex CS)-Clinical Monitoring Results </t>
+          <t>Hill-Rom/Welch Allyn (Connex CS)-PCSCMI</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Admissions </t>
+          <t>Hospira (Theradoc)-ADMO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS DI Results </t>
+          <t>Hospira (Theradoc)-ITSDIRO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-ITS HM Results </t>
+          <t>Hospira (Theradoc)-ITSHMRO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Lab Results (Discrete) </t>
+          <t>Hospira (Theradoc)-LABRES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-OM Orders </t>
+          <t>Hospira (Theradoc)-OMORDO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospira (Theradoc)-Pharmacy Orders </t>
+          <t>Hospira (Theradoc)-PHAORD</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople ED Patient Visit Data</t>
+          <t>Hospira (Theradoc)-iPeople EDM</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Medication Administration</t>
+          <t>Hospira (Theradoc)-iPeople Meds</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hospira (Theradoc)-iPeople Nursing Assessment Forms</t>
+          <t>Hospira (Theradoc)-iPeople PCS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -15568,7 +15568,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase RX-ADT/Link Orders)-Admissions </t>
+          <t>Hyland (Onbase RX-ADT/Link Orders)-ADMO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Hyland (Onbase to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyland (Onbase)-Admissions </t>
+          <t>Hyland (Onbase)-ADMO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBM (Consent Management)-Admissions </t>
+          <t>IBM (Consent Management)-ADMO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Admissions </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-ADMO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS Integrated Medical Systems (ReadyTracker-Tissue)-Tissue Tracking </t>
+          <t>IMS Integrated Medical Systems (ReadyTracker-Tissue)-SURTSD</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -16437,7 +16437,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiate (Initiate)-Admissions </t>
+          <t>Initiate (Initiate)-ADMO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-</t>
+          <t>Iodine Software (Iodine-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16627,6 +16627,21 @@
       <c r="P212" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -16648,7 +16663,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Admissions </t>
+          <t>Iodine Software (Iodine-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -16698,17 +16713,17 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -16730,7 +16745,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS DI Results </t>
+          <t>Iodine Software (Iodine-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16780,7 +16795,7 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -16790,7 +16805,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -16812,7 +16827,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-ITS HM Results </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16862,7 +16877,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -16872,7 +16887,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -16894,7 +16909,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Lab Results (Discrete) </t>
+          <t>Iodine Software (Iodine-Facility)-LABRES2</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -16944,7 +16959,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -16954,7 +16969,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -16976,7 +16991,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-OM Orders </t>
+          <t>Iodine Software (Iodine-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -17058,7 +17073,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Iodine Software (Iodine-Facility)-Pathology Results</t>
+          <t>Iodine Software (Iodine-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -17108,17 +17123,17 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17140,7 +17155,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iodine Software (Iodine-Facility)-Pharmacy Orders </t>
+          <t>Iodine Software (Iodine-Facility)-radord</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -17186,21 +17201,6 @@
       <c r="P219" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R219" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">IsoPrime (NeoData)-Admissions </t>
+          <t>IsoPrime (NeoData)-ADMO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">IsoPrime (NeoData)-ITS HM Results </t>
+          <t>IsoPrime (NeoData)-ITSHMRO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">IsoPrime (NeoData)-Lab Results (Discrete) </t>
+          <t>IsoPrime (NeoData)-LABRES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-Admissions </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ADMO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">MSN Healthcare Solutions (Intellirad)-ITS DI Results </t>
+          <t>MSN Healthcare Solutions (Intellirad)-ITSDIRO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>McKesson (MPF-Patient Folder/HPF Facility to SMART)-</t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility to SMART)-bill</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKesson (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>McKesson (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Medaxion (Medaxion Pulse to MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Admissions </t>
+          <t>Medaxion (Medaxion Pulse)-ADMO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medaxion (Medaxion Pulse)-Scheduling </t>
+          <t>Medaxion (Medaxion Pulse)-CWSO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-</t>
+          <t>Meditech (HCA 5.6)-ADMO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -18507,6 +18507,21 @@
       <c r="P237" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -18528,7 +18543,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Admissions </t>
+          <t>Meditech (HCA 5.6)-ITSDIRO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -18578,17 +18593,17 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -18610,7 +18625,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS DI Results </t>
+          <t>Meditech (HCA 5.6)-ITSHMRO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -18660,7 +18675,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>ITSDIRO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -18670,7 +18685,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS DI Results </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -18692,7 +18707,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-ITS HM Results </t>
+          <t>Meditech (HCA 5.6)-LABRES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -18742,7 +18757,7 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>LABRES</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -18752,7 +18767,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Lab Results (Discrete) </t>
         </is>
       </c>
     </row>
@@ -18774,7 +18789,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Lab Results (Discrete) </t>
+          <t>Meditech (HCA 5.6)-LABRES2</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -18824,7 +18839,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>LABRES</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -18834,7 +18849,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lab Results (Discrete) </t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -18856,7 +18871,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-OM Orders </t>
+          <t>Meditech (HCA 5.6)-OMORDO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -18938,7 +18953,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Meditech (HCA 5.6)-Pathology Results</t>
+          <t>Meditech (HCA 5.6)-PHAORD</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -18988,17 +19003,17 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -19020,7 +19035,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (HCA 5.6)-Pharmacy Orders </t>
+          <t>Meditech (HCA 5.6)-radord</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -19066,21 +19081,6 @@
       <c r="P244" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q244" t="inlineStr">
-        <is>
-          <t>PHAORD</t>
-        </is>
-      </c>
-      <c r="R244" t="inlineStr">
-        <is>
-          <t>RDE</t>
-        </is>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Admissions </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ADMO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS DI Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-ITS HM Results </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meditech (MPF-Patient Folder/HPF Facility)-Scanned Documents </t>
+          <t>Meditech (MPF-Patient Folder/HPF Facility)-SCAIMG</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -19636,7 +19636,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mednax (BabySteps Cloud)-Admissions </t>
+          <t>Mednax (BabySteps Cloud)-ADMO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-Admissions </t>
+          <t>Midas+ (Care Management-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS DI Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -20026,7 +20026,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midas+ (Care Management-Facility)-ITS HM Results </t>
+          <t>Midas+ (Care Management-Facility)-ITSHMRO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Admissions </t>
+          <t>Mobile Heartbeat (imobile)-ADMO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -20334,7 +20334,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Heartbeat (imobile)-Lab Results (Discrete) </t>
+          <t>Mobile Heartbeat (imobile)-LABRES</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -20478,7 +20478,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Admissions </t>
+          <t>Net Health (ReDoc Xfit)-ADMO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-Charges </t>
+          <t>Net Health (ReDoc Xfit)-ITSHMRO</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -20610,17 +20610,17 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>Patient Accounting</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charges </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-ITS HM Results </t>
+          <t>Net Health (ReDoc Xfit)-OMORDO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -20687,22 +20687,22 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>OMORDO</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>ORM</t>
         </is>
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">OM Orders </t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Net Health (ReDoc Xfit)-OM Orders </t>
+          <t>Net Health (ReDoc Xfit)-Patient Accounting</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -20769,22 +20769,22 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>OMORDO</t>
+          <t>Patient Accounting</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>ORM</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">OM Orders </t>
+          <t xml:space="preserve">Charges </t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Nuance (Primordial)-</t>
+          <t>Nuance (Primordial)-ADMO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -20914,6 +20914,21 @@
       <c r="P268" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -20935,7 +20950,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuance (Primordial)-Admissions </t>
+          <t>Nuance (Primordial)-ITSDIRO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -20985,17 +21000,17 @@
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>ITSDIRO</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -21017,7 +21032,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nuance (Primordial)-ITS DI Results </t>
+          <t>Nuance (Primordial)-radord</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -21063,21 +21078,6 @@
       <c r="P270" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>ITSDIRO</t>
-        </is>
-      </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS DI Results </t>
         </is>
       </c>
     </row>
@@ -21161,7 +21161,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Omnicell (Optiflex to SMART)-</t>
+          <t>Omnicell (Optiflex to SMART)-mmrepl</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Admissions </t>
+          <t>Omnicell (Optiflex)-ADMO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omnicell (Optiflex)-Charges </t>
+          <t>Omnicell (Optiflex)-Patient Accounting</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport Health Communications, Inc. (eCare Next)-Admissions </t>
+          <t>Passport Health Communications, Inc. (eCare Next)-ADMO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Patient Keeper (Portal)-</t>
+          <t>Patient Keeper (Portal)-ITSHMRO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -21706,6 +21706,21 @@
       <c r="P279" t="inlineStr">
         <is>
           <t>Inbound</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>ITSHMRO</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>ORU</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -21727,7 +21742,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patient Keeper (Portal)-ITS HM Results </t>
+          <t>Patient Keeper (Portal)-eps</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -21773,21 +21788,6 @@
       <c r="P280" t="inlineStr">
         <is>
           <t>Inbound</t>
-        </is>
-      </c>
-      <c r="Q280" t="inlineStr">
-        <is>
-          <t>ITSHMRO</t>
-        </is>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>ORU</t>
-        </is>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (Apex to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Admissions </t>
+          <t>Provation (Apex)-ADMO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-ITS HM Results </t>
+          <t>Provation (Apex)-CWSO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -22127,22 +22127,22 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Inbound</t>
+          <t>Outbound</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>ITSHMRO</t>
+          <t>CWSO</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>SIU</t>
         </is>
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITS HM Results </t>
+          <t xml:space="preserve">Scheduling </t>
         </is>
       </c>
     </row>
@@ -22164,7 +22164,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (Apex)-Scheduling </t>
+          <t>Provation (Apex)-ITSHMRO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -22209,22 +22209,22 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>CWSO</t>
+          <t>ITSHMRO</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>SIU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduling </t>
+          <t xml:space="preserve">ITS HM Results </t>
         </is>
       </c>
     </row>
@@ -22308,7 +22308,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE to MD - CMORE)-ITS HM Results </t>
+          <t>Provation (MD - CMORE to MD - CMORE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-</t>
+          <t>Provation (MD - CMORE to MPF-Patient Folder/HPF Facility)-imgurl</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-Admissions </t>
+          <t>Provation (MD - CMORE)-ADMO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -22663,7 +22663,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provation (MD - CMORE)-ITS HM Results </t>
+          <t>Provation (MD - CMORE)-ITSHMRO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -22807,7 +22807,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rauland (Responder)-Admissions </t>
+          <t>Rauland (Responder)-ADMO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Siemens (RapidComm)-Admissions </t>
+          <t>Siemens (RapidComm)-ADMO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sisco (FastPass)-Admissions </t>
+          <t>Sisco (FastPass)-ADMO</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -23239,7 +23239,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team Health (Team Health)-Admissions </t>
+          <t>Team Health (Team Health)-ADMO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Telcor (Quick-Link to Quick-Link)-</t>
+          <t>Telcor (Quick-Link to Quick-Link)-ADMO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -23429,6 +23429,21 @@
       <c r="P303" t="inlineStr">
         <is>
           <t>CHECK THIS ROW</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -23450,7 +23465,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telcor (Quick-Link to Quick-Link)-Admissions </t>
+          <t>Telcor (Quick-Link to Quick-Link)-labpoc</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -23496,21 +23511,6 @@
       <c r="P304" t="inlineStr">
         <is>
           <t>CHECK THIS ROW</t>
-        </is>
-      </c>
-      <c r="Q304" t="inlineStr">
-        <is>
-          <t>ADMO</t>
-        </is>
-      </c>
-      <c r="R304" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="S304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -23594,7 +23594,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telcor (Quick-Link)-Admissions </t>
+          <t>Telcor (Quick-Link)-ADMO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-Admissions </t>
+          <t>TeleSpecialists (TeleCare)-ADMO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-ITS HM Results </t>
+          <t>TeleSpecialists (TeleCare)-ITSHMRO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleSpecialists (TeleCare)-OM Orders </t>
+          <t>TeleSpecialists (TeleCare)-OMORDO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-Admissions </t>
+          <t>TeleTracking (TransferCenter IQ)-ADMO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">TeleTracking (TransferCenter IQ)-OM Orders </t>
+          <t>TeleTracking (TransferCenter IQ)-OMORDO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>TeleTracking (TransferCenter IQ)-iPeople Nursing Assessment Forms</t>
+          <t>TeleTracking (TransferCenter IQ)-iPeople PCS</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -24354,7 +24354,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telexy Healthcare Inc (Q-path)-Admissions </t>
+          <t>Telexy Healthcare Inc (Q-path)-ADMO</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Ventana Medical Systems (VANTAGE)-</t>
+          <t>Ventana Medical Systems (VANTAGE)-pthord</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Admissions </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ADMO</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITS DI Results </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-ITSDIRO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Lab Results (Discrete) </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-LABRES</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -24873,7 +24873,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -24955,7 +24955,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OM Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-OMORDO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -25037,7 +25037,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-Pharmacy Orders </t>
+          <t>VigiLanz Corp (Dynamic PharmacoVigilance-Facility)-PHAORD</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Volpara Health (Aspen Breast)-</t>
+          <t>Volpara Health (Aspen Breast)-radord</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-</t>
+          <t>dbMotion (db Motion)-ADMO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -25356,6 +25356,21 @@
       <c r="P329" t="inlineStr">
         <is>
           <t>Outbound</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>ADMO</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admissions </t>
         </is>
       </c>
     </row>
@@ -25377,7 +25392,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Admissions </t>
+          <t>dbMotion (db Motion)-IMMUN</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -25427,17 +25442,17 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>ADMO</t>
+          <t>IMMUN</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>VXU</t>
         </is>
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admissions </t>
+          <t>MU-Immunizations</t>
         </is>
       </c>
     </row>
@@ -25459,7 +25474,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS DI Results </t>
+          <t>dbMotion (db Motion)-ITSDIRO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -25541,7 +25556,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-ITS HM Results </t>
+          <t>dbMotion (db Motion)-ITSHMRO</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -25623,7 +25638,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Lab Results (Discrete) </t>
+          <t>dbMotion (db Motion)-LABRES</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -25705,7 +25720,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-MU-Immunizations</t>
+          <t>dbMotion (db Motion)-LABRES2</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -25755,17 +25770,17 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>IMMUN</t>
+          <t>LABRES2</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>VXU</t>
+          <t>ORU</t>
         </is>
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>MU-Immunizations</t>
+          <t>Pathology Results</t>
         </is>
       </c>
     </row>
@@ -25787,7 +25802,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-Pathology Results</t>
+          <t>dbMotion (db Motion)-PHAORD</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -25837,17 +25852,17 @@
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>LABRES2</t>
+          <t>PHAORD</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>ORU</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>Pathology Results</t>
+          <t xml:space="preserve">Pharmacy Orders </t>
         </is>
       </c>
     </row>
@@ -25869,7 +25884,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">dbMotion (db Motion)-Pharmacy Orders </t>
+          <t>dbMotion (db Motion)-iPeople EDM</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -25919,17 +25934,17 @@
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>PHAORD</t>
+          <t>iPeople EDM</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>EDM - iPeople</t>
         </is>
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacy Orders </t>
+          <t>iPeople ED Patient Visit Data</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25966,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople ED Patient Visit Data</t>
+          <t>dbMotion (db Motion)-iPeople PCS</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -26001,17 +26016,17 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>iPeople EDM</t>
+          <t>iPeople PCS</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>EDM - iPeople</t>
+          <t>PCS - iPeople</t>
         </is>
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>iPeople ED Patient Visit Data</t>
+          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -26033,7 +26048,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>dbMotion (db Motion)-iPeople Nursing Assessment Forms</t>
+          <t>dbMotion (db Motion)-radord</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -26079,21 +26094,6 @@
       <c r="P338" t="inlineStr">
         <is>
           <t>Outbound</t>
-        </is>
-      </c>
-      <c r="Q338" t="inlineStr">
-        <is>
-          <t>iPeople PCS</t>
-        </is>
-      </c>
-      <c r="R338" t="inlineStr">
-        <is>
-          <t>PCS - iPeople</t>
-        </is>
-      </c>
-      <c r="S338" t="inlineStr">
-        <is>
-          <t>iPeople Nursing Assessment Forms</t>
         </is>
       </c>
     </row>
@@ -26177,7 +26177,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (HCA 5.6)-iPeople EDM</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -26259,7 +26259,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>iPeople (HCA 5.6)-iPeople Medication Administration</t>
+          <t>iPeople (HCA 5.6)-iPeople Meds</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -26403,7 +26403,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">iPeople (iPeople MT56)-OM Orders </t>
+          <t>iPeople (iPeople MT56)-OMORDO</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople ED Patient Visit Data</t>
+          <t>iPeople (iPeople MT56)-iPeople EDM</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -26567,7 +26567,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Medication Administration</t>
+          <t>iPeople (iPeople MT56)-iPeople Meds</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>iPeople (iPeople MT56)-iPeople Nursing Assessment Forms</t>
+          <t>iPeople (iPeople MT56)-iPeople PCS</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
